--- a/zayavki/2026-10-29_Заявка_1.xlsx
+++ b/zayavki/2026-10-29_Заявка_1.xlsx
@@ -550,7 +550,7 @@
         <v>6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>301850</v>
+        <v>332035</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,7 +564,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>328806</v>
+        <v>361687</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -578,7 +578,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>328806</v>
+        <v>361687</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -592,7 +592,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>272199</v>
+        <v>299419</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -606,7 +606,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>274895</v>
+        <v>302384</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,7 +620,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>272199</v>
+        <v>299419</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,7 +634,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>539061</v>
+        <v>592967</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -648,7 +648,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>537443</v>
+        <v>591188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -662,7 +662,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>549843</v>
+        <v>604827</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -674,7 +674,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>539061</v>
+        <v>592967</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>571408</v>
+        <v>628549</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -702,7 +702,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>522887</v>
+        <v>575176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -714,7 +714,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>506229</v>
+        <v>556852</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -728,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>646884</v>
+        <v>711572</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -742,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>619928</v>
+        <v>681921</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -756,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>619928</v>
+        <v>681921</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -770,7 +770,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>619928</v>
+        <v>681921</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -784,7 +784,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>646884</v>
+        <v>711572</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
